--- a/public/templates/Statement_Template.xlsx
+++ b/public/templates/Statement_Template.xlsx
@@ -87,12 +87,6 @@
     <t>Gross Salary</t>
   </si>
   <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Full Name</t>
-  </si>
-  <si>
     <t>Payslip Generated</t>
   </si>
   <si>
@@ -102,38 +96,44 @@
     <t>Payslip Generation</t>
   </si>
   <si>
-    <t>STS001</t>
-  </si>
-  <si>
-    <t>Rahul Sharma</t>
-  </si>
-  <si>
     <t>Approved</t>
   </si>
   <si>
     <t>disabled</t>
   </si>
   <si>
-    <t>STS002</t>
-  </si>
-  <si>
     <t>Priya Patel</t>
   </si>
   <si>
-    <t>STS003</t>
-  </si>
-  <si>
     <t>Amit Kumar</t>
   </si>
   <si>
     <t>Pending</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>STS-000012</t>
+  </si>
+  <si>
+    <t>Rohit Sharma</t>
+  </si>
+  <si>
+    <t>STS-000014</t>
+  </si>
+  <si>
+    <t>STS-000019</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,80 +141,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF002060"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -222,64 +158,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -586,7 +471,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -620,12 +505,12 @@
     <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.6">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -633,159 +518,159 @@
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="X1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1">
         <v>600000</v>
       </c>
-      <c r="D2" s="11">
-        <v>30000</v>
-      </c>
-      <c r="E2" s="12">
-        <v>12000</v>
-      </c>
-      <c r="F2" s="11">
-        <v>3000</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5000</v>
-      </c>
-      <c r="H2" s="11">
-        <v>2000</v>
-      </c>
-      <c r="I2" s="11">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11">
-        <v>2500</v>
-      </c>
-      <c r="K2" s="11">
-        <v>3000</v>
-      </c>
-      <c r="L2" s="11">
-        <v>0</v>
-      </c>
-      <c r="M2" s="11">
+      <c r="D2" s="1">
+        <v>25000</v>
+      </c>
+      <c r="E2" s="1">
+        <v>12500</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8597.5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>5000000</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
         <v>1800</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="1">
         <v>1800</v>
       </c>
-      <c r="O2" s="11">
-        <v>750</v>
-      </c>
-      <c r="P2" s="11">
-        <v>1250</v>
-      </c>
-      <c r="Q2" s="11">
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1202.5</v>
+      </c>
+      <c r="Q2" s="1">
         <v>200</v>
       </c>
-      <c r="R2" s="11">
-        <v>1500</v>
-      </c>
-      <c r="S2" s="11">
-        <v>500</v>
-      </c>
-      <c r="T2" s="11">
-        <v>0</v>
-      </c>
-      <c r="U2" s="13">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>45750</v>
-      </c>
-      <c r="W2">
-        <v>42000</v>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>5046097.5</v>
+      </c>
+      <c r="W2" s="1">
+        <v>5044097.5</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" t="s">
-        <v>30</v>
+      <c r="A3" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>950000</v>
@@ -854,18 +739,18 @@
         <v>0</v>
       </c>
       <c r="Y3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" t="s">
-        <v>32</v>
+      <c r="A4" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>480000</v>
@@ -934,10 +819,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
